--- a/InputData/elec/GDPbES/Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/GDPbES/Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -1,21 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI - units progress\InputData\elec\GDPbES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daiyang.zhang\Desktop\eps-us-3.4.7 working_D1904_T0858_woking\eps-us-3.4.7 HK working\InputData\elec\GDPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83509DFB-9114-4D9E-9DB2-B0074854561B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="90" windowWidth="22995" windowHeight="11055"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="GDPbES" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -124,7 +138,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -189,9 +203,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -229,9 +243,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -266,7 +280,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -301,7 +315,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -474,86 +488,86 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -565,18 +579,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AK17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.1796875" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>32</v>
       </c>
@@ -689,7 +703,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -837,1191 +851,1191 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:R14" si="1">$B3</f>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="O3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="R3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="T3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="U3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="V3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="W3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="X3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Y3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Z3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AA3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AB3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AC3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AD3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AE3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AF3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AG3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AH3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AI3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AJ3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AK3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Z4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Z5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>27</v>
       </c>
       <c r="B6">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="T6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="U6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="X6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Y6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Z6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AA6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AB6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AC6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AD6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AF6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AG6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AH6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AI6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AK6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="T7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="U7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="X7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Y7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Z7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AA7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AB7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AC7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AD7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AF7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AG7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AH7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AI7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AK7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="T8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="U8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="X8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Y8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Z8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AA8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AB8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AC8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AD8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AF8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AG8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AH8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AI8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AK8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Z9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <f t="shared" ref="D9:AK14" si="2">$B9</f>
-        <v>0.5</v>
+        <f t="shared" ref="AJ9:AK9" si="2">$B9</f>
+        <v>0</v>
       </c>
       <c r="AK9">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="E10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="F10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="J10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="K10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="L10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="M10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="N10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="O10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="P10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="R10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="S10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" ref="S10:AK14" si="3">$B10</f>
+        <v>0</v>
       </c>
       <c r="T10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="U10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="V10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="W10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="X10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -2033,143 +2047,143 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -2181,143 +2195,143 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -2325,147 +2339,147 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <f t="shared" si="1"/>
+        <f>$B13</f>
         <v>0</v>
       </c>
       <c r="D13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -2473,591 +2487,483 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <f t="shared" si="1"/>
+        <f>$B14</f>
         <v>0</v>
       </c>
       <c r="D14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15">
-        <f>B11</f>
         <v>0</v>
       </c>
       <c r="C15">
-        <f t="shared" ref="C15:AK15" si="3">C11</f>
         <v>0</v>
       </c>
       <c r="D15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK15">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16">
-        <f>B11</f>
         <v>0</v>
       </c>
       <c r="C16">
-        <f t="shared" ref="C16:AK16" si="4">C11</f>
         <v>0</v>
       </c>
       <c r="D16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="U16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="V16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Y16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Z16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AC16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AD16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AE16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AF16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AG16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AH16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AI16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AJ16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AK16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17">
-        <f>B9</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <f t="shared" ref="C17:AK17" si="5">C9</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3066,31 +2972,41 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3098,24 +3014,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -3134,70 +3111,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -3299,32 +3229,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70EDE735-2610-4C1E-AFBA-21B0312DA583}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3223AC9D-A569-40AC-A845-5B19FB05EC42}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E98BEC28-D95F-42E6-8AE9-0B55BF1DCB36}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D87BD64D-B710-4384-B390-FCBE7D0E11F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B7E2E01-5A0C-468A-A3A7-BA67E754D343}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <ds:schemaRef ds:uri="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>